--- a/methods/称量记录模板.xlsx
+++ b/methods/称量记录模板.xlsx
@@ -1,84 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Agent\lims数据登记\methods\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89876D15-D3C4-4C58-8E8C-AD72F2D6395F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="称量记录" sheetId="1" r:id="rId1"/>
+    <sheet name="称量记录" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>称样时间</t>
-  </si>
-  <si>
-    <t>样品编号</t>
-  </si>
-  <si>
-    <t>试样描述</t>
-  </si>
-  <si>
-    <t>解析</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>红色颗粒</t>
-  </si>
-  <si>
-    <t>浸泡面积s (cm2)</t>
-  </si>
-  <si>
-    <t>50%乙醇：40℃，10d；填充法，填充体积为220mL；第1次测试结果</t>
-  </si>
-  <si>
-    <t>TS26081242001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 浸泡体积V (mL)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -96,26 +48,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,64 +411,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="17.9296875" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" customWidth="1"/>
-    <col min="7" max="7" width="46.59765625" style="2" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>称样时间</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>样品编号</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>检测项目</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>试样描述</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>称样量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>测量1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>测量2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>110</v>
-      </c>
-      <c r="E2">
-        <v>120</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TN26080726001M</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>红色颗粒</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>M=标记样；解析列填「解析」=强制解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TN26080726001A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>红色颗粒</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5274</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A/B=平行样，行序即平行序</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TN26080726001B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>红色颗粒</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.39/10.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>斜杠后=定容体积</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TN26080726002A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>胶水</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>称样量留空=随机生成后回写</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TN26080726003A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>检测项目名称</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>面层</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>检测项目填 LIMS 项目名按名称匹配路由；同条件多变体可写 项目名|条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TN26080726004A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>面层</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>测量1/测量2=同名列示例：列名与 LIMS 动态列同名即按行序自动填值，可加任意列</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>